--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
+          <t>HSV položkově (121 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 134 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 33 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 37 sklad = 238 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>234 (201 dum + 33 sklad)</t>
+          <t>238 (201 dum + 37 sklad)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 121 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 35 | 0.90: 32 | 0.85: 41 | 0.80: 21 | 0.75: 70 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 32 | 0.85: 45 | 0.80: 21 | 0.75: 70 | 0.70: 7 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 157 needs_production_lookup (67.1 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 161 needs_production_lookup (67.6 %)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>31 items (viz Otazky_pro_Karla docx)</t>
+          <t>34 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1182,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 35×0.95 · 32×0.90 · 41×0.85 · 21×0.80 · 70×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+238 položek celkem (201 dum + 37 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 32×0.90 · 45×0.85 · 21×0.80 · 70×0.75 · 7×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1255,7 +1255,7 @@
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>• Total items: 234 (201 dům + 33 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 71 items s realizuje_skladbu.</t>
+          <t>• Total items: 238 (201 dům + 37 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 72 items s realizuje_skladbu.</t>
         </is>
       </c>
     </row>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Sejmutí stávající zídky + schodiště; Hloubení figury skladu; Hloubení rýh pro pasy; Hloubení parkingových patek; … (+2 dalších)</t>
+          <t>Sejmutí stávající zídky + schodiště; Hloubení figury skladu; Hloubení rýh pro pasy; Hloubení parkingových patek; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="10" t="n"/>
       <c r="F2" s="10" t="n"/>
@@ -3131,11 +3131,11 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); Zábradlí stání</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
@@ -3207,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n"/>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu — Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + zalití C25/30</t>
+          <t>Tvarovky ZB obvod skladu — Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="F43" s="22" t="n">
-        <v>46.5</v>
+        <v>62.5</v>
       </c>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="F44" s="22" t="n">
-        <v>1398</v>
+        <v>1875</v>
       </c>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="10" t="n"/>
@@ -8033,34 +8033,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C121" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>Kladecí lože pod dlažbu — Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skladu</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F121" s="22" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="G121" s="10" t="n"/>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 564231111</t>
         </is>
       </c>
     </row>
@@ -8073,34 +8073,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C122" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Zásyp za prefa opěrnou stěnou — Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuveden v legendě, OVĚŘIT)</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F122" s="22" t="n">
+        <v>23.5</v>
       </c>
       <c r="G122" s="10" t="n"/>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 174101101</t>
         </is>
       </c>
     </row>
@@ -8115,12 +8115,12 @@
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8150,17 +8150,17 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8190,17 +8190,17 @@
       </c>
       <c r="B125" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="C132" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C133" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
@@ -8544,8 +8544,88 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="20" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C134" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E134" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="10" t="n"/>
+      <c r="H134" s="10" t="n"/>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J134" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C135" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E135" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="10" t="n"/>
+      <c r="H135" s="10" t="n"/>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J135" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J133"/>
+  <autoFilter ref="A1:J135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22387,7 +22467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -22800,7 +22880,7 @@
         </is>
       </c>
       <c r="G6" s="22" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n"/>
@@ -22810,7 +22890,7 @@
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
@@ -22819,7 +22899,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>DXF podlaha skladu 6.35×3.34 = 21.2 m²</t>
+          <t>legenda místností 17.6 m² + vynos S01 za stěnu 6010×1000 mm dle řezu B-B (neviditelný na půdorysu)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -22839,7 +22919,7 @@
       </c>
       <c r="Q6" s="41" t="inlineStr">
         <is>
-          <t>W1_PODLAHA_17.6_2026-06-01</t>
+          <t>S01_AREA_23.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -22917,22 +22997,22 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>HSV-2 Základové a ŽB</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy sklad</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>271313??? ?</t>
+          <t>Kladecí lože pod dlažbu</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>564231111</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
+          <t>Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skladu</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -22941,26 +23021,26 @@
         </is>
       </c>
       <c r="G8" s="22" t="n">
-        <v>4.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H8" s="10" t="n"/>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ + TZ statika sklad §4 — C16/20 XC0 pasy 500×500</t>
+          <t>skladba S01 — kladecí vrstva kamenná drť 4-8 mm 40 mm (vrstva dříve chyběla)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -22968,14 +23048,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O8" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
       <c r="P8" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S01_sklad</t>
         </is>
       </c>
       <c r="Q8" s="41" t="n"/>
@@ -22986,55 +23066,55 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>HSV-2 Základové a ŽB</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — spodní</t>
+          <t>Zásyp za prefa opěrnou stěnou</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>273313811</t>
+          <t>174101101</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
+          <t>Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuveden v legendě, OVĚŘIT)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>6</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>23.5</v>
       </c>
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="L9" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
+          <t>řez A-A — klín zásypu za S04; materiál v legendě NEuveden → OVĚŘIT</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>#36</t>
         </is>
       </c>
       <c r="O9" s="26" t="inlineStr">
@@ -23042,12 +23122,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P9" s="41" t="n"/>
-      <c r="Q9" s="41" t="inlineStr">
-        <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P9" s="41" t="inlineStr"/>
+      <c r="Q9" s="41" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -23060,26 +23136,26 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — horní</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>311233812</t>
+          <t>Základové pasy sklad</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>271313??? ?</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>6</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>4.84</v>
       </c>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
@@ -23093,12 +23169,12 @@
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
+          <t>DXF sklad_DPZ + TZ statika sklad §4 — C16/20 XC0 pasy 500×500</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -23106,17 +23182,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O10" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P10" s="41" t="n"/>
-      <c r="Q10" s="41" t="inlineStr">
-        <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="O10" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P10" s="41" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S03b_sklad</t>
+        </is>
+      </c>
+      <c r="Q10" s="41" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -23129,26 +23205,26 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Beton patek + zídek — zalití</t>
+          <t>Patky parking — spodní</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>273321321</t>
+          <t>273313811</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
+          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>1.75</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>6</v>
       </c>
       <c r="H11" s="10" t="n"/>
       <c r="I11" s="10" t="n"/>
@@ -23158,21 +23234,21 @@
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 (6 patek)</t>
+          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O11" s="26" t="inlineStr">
@@ -23198,32 +23274,32 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože</t>
+          <t>Patky parking — horní</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>174101101</t>
+          <t>311233812</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>1.76</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>6</v>
       </c>
       <c r="H12" s="10" t="n"/>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>zemni_prace</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
@@ -23231,12 +23307,12 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_cross_discipline_legitimate</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>DXF + TZ statika sklad</t>
+          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -23249,14 +23325,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P12" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad, S05_sklad</t>
-        </is>
-      </c>
+      <c r="P12" s="41" t="n"/>
       <c r="Q12" s="41" t="inlineStr">
         <is>
-          <t>W1_PODLAHA_17.6_2026-06-01</t>
+          <t>PATKY_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23271,17 +23343,17 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Schodišťová deska + pas</t>
+          <t>Beton patek + zídek — zalití</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273321321</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -23290,7 +23362,7 @@
         </is>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n"/>
@@ -23309,7 +23381,7 @@
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — prefa schodové dílce + ŽB pas</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 (6 patek)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -23322,12 +23394,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P13" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
-      <c r="Q13" s="41" t="n"/>
+      <c r="P13" s="41" t="n"/>
+      <c r="Q13" s="41" t="inlineStr">
+        <is>
+          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -23335,50 +23407,50 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna</t>
+          <t>Štěrkopískové lože</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>311233815</t>
+          <t>174101101</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="n">
-        <v>18</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>1.76</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_cross_discipline_legitimate</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+          <t>DXF + TZ statika sklad</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23393,12 +23465,12 @@
       </c>
       <c r="P14" s="41" t="inlineStr">
         <is>
-          <t>S04_sklad</t>
+          <t>S01_sklad, S05_sklad</t>
         </is>
       </c>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
+          <t>W1_PODLAHA_17.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23408,41 +23480,41 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu</t>
+          <t>Schodišťová deska + pas</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>311233811</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + zalití C25/30</t>
+          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>46.5</v>
+        <v>0.8</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -23451,7 +23523,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION obvod</t>
+          <t>TZ statika sklad §4 — prefa schodové dílce + ŽB pas</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23466,7 +23538,7 @@
       </c>
       <c r="P15" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S05_sklad</t>
         </is>
       </c>
       <c r="Q15" s="41" t="n"/>
@@ -23482,50 +23554,50 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>1398</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>18</v>
       </c>
       <c r="H16" s="10" t="n"/>
       <c r="I16" s="10" t="n"/>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity Methvin — výztuž do ZB tvarovek tl. 250 mm</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O16" s="26" t="inlineStr">
@@ -23535,12 +23607,12 @@
       </c>
       <c r="P16" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S04_sklad</t>
         </is>
       </c>
       <c r="Q16" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23555,17 +23627,17 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
+          <t>Tvarovky ZB obvod skladu</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311233811</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -23574,17 +23646,17 @@
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -23593,7 +23665,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -23608,12 +23680,12 @@
       </c>
       <c r="P17" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q17" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23628,50 +23700,49 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
+          <t>Výztuž ZB tvarovek</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G18" s="22" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04</t>
-        </is>
+          <t>family_verified_leaf_needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M18" s="8">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="O18" s="26" t="inlineStr">
@@ -23681,12 +23752,12 @@
       </c>
       <c r="P18" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q18" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23696,41 +23767,41 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>36.74</v>
+        <v>33</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
@@ -23739,7 +23810,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -23754,12 +23825,12 @@
       </c>
       <c r="P19" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q19" s="41" t="inlineStr">
         <is>
-          <t>DS3_STROPNICE_11_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23769,22 +23840,22 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -23793,17 +23864,17 @@
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>21.209</v>
+        <v>33</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
@@ -23812,7 +23883,7 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -23827,10 +23898,14 @@
       </c>
       <c r="P20" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="Q20" s="41" t="n"/>
+          <t>S03a_sklad, S04_sklad</t>
+        </is>
+      </c>
+      <c r="Q20" s="41" t="inlineStr">
+        <is>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -23843,32 +23918,32 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>22.26945</v>
+        <v>36.74</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
@@ -23881,7 +23956,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — HI souvrství</t>
+          <t>TZ statika sklad §4 + DXF DIMENSION</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -23899,7 +23974,11 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q21" s="41" t="n"/>
+      <c r="Q21" s="41" t="inlineStr">
+        <is>
+          <t>DS3_STROPNICE_11_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -23912,36 +23991,36 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>790</v>
+        <v>21.209</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
@@ -23950,12 +24029,12 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+          <t>TZ statika sklad §4 + DXF</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O22" s="26" t="inlineStr">
@@ -23968,11 +24047,7 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q22" s="41" t="inlineStr">
-        <is>
-          <t>IPE_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="Q22" s="41" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n">
@@ -23985,17 +24060,17 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -24004,26 +24079,26 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>44.6</v>
+        <v>22.26945</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §4 — HI souvrství</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -24041,11 +24116,7 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q23" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q23" s="41" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="20" t="n">
@@ -24058,17 +24129,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -24077,7 +24148,7 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
@@ -24087,20 +24158,21 @@
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M24" s="8">
-        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
-        <v/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+        </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O24" s="26" t="inlineStr">
@@ -24125,22 +24197,22 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -24149,26 +24221,26 @@
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -24183,12 +24255,12 @@
       </c>
       <c r="P25" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q25" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -24198,49 +24270,50 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G26" s="22" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="n">
+        <v>1420</v>
+      </c>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
-        </is>
+      <c r="M26" s="8">
+        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
+        <v/>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
@@ -24252,10 +24325,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P26" s="41" t="inlineStr"/>
+      <c r="P26" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
       <c r="Q26" s="41" t="inlineStr">
         <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+          <t>IPE_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24265,41 +24342,41 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Sklad mezipodesta schodiště prefa</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
@@ -24308,7 +24385,7 @@
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24321,8 +24398,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P27" s="41" t="n"/>
-      <c r="Q27" s="41" t="n"/>
+      <c r="P27" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q27" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="n">
@@ -24330,12 +24415,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -24345,26 +24430,24 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G28" s="23" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="n"/>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
@@ -24373,7 +24456,7 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -24399,50 +24482,50 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G29" s="22" t="n">
-        <v>17.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24450,21 +24533,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O29" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P29" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q29" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
-        </is>
-      </c>
+      <c r="O29" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P29" s="41" t="n"/>
+      <c r="Q29" s="41" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="n">
@@ -24472,41 +24547,41 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Oplocení (plot)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>3.8</v>
       </c>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
@@ -24515,12 +24590,12 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#37</t>
         </is>
       </c>
       <c r="O30" s="26" t="inlineStr">
@@ -24528,7 +24603,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P30" s="41" t="n"/>
+      <c r="P30" s="41" t="inlineStr"/>
       <c r="Q30" s="41" t="n"/>
     </row>
     <row r="31">
@@ -24537,41 +24612,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
+          <t>Zábradlí stání</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -24580,12 +24655,12 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#38</t>
         </is>
       </c>
       <c r="O31" s="26" t="inlineStr">
@@ -24593,7 +24668,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P31" s="41" t="n"/>
+      <c r="P31" s="41" t="inlineStr"/>
       <c r="Q31" s="41" t="n"/>
     </row>
     <row r="32">
@@ -24602,27 +24677,27 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G32" s="23" t="n">
@@ -24632,11 +24707,11 @@
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
@@ -24645,7 +24720,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -24658,8 +24733,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P32" s="41" t="n"/>
-      <c r="Q32" s="41" t="n"/>
+      <c r="P32" s="41" t="inlineStr"/>
+      <c r="Q32" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n">
@@ -24667,50 +24746,50 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="n">
+        <v>23.6</v>
       </c>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K33" s="24" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="L33" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -24718,15 +24797,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O33" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P33" s="41" t="inlineStr"/>
+      <c r="O33" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P33" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
       <c r="Q33" s="41" t="inlineStr">
         <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+          <t>S01_AREA_23.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24736,27 +24819,27 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G34" s="23" t="n">
@@ -24766,11 +24849,11 @@
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K34" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L34" s="20" t="inlineStr">
         <is>
@@ -24779,7 +24862,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -24795,9 +24878,273 @@
       <c r="P34" s="41" t="n"/>
       <c r="Q34" s="41" t="n"/>
     </row>
+    <row r="35">
+      <c r="A35" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace odpadu sklad</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>997013211</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>bourani_demolice</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+        </is>
+      </c>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O35" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P35" s="41" t="n"/>
+      <c r="Q35" s="41" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>030141000</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K36" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+        </is>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O36" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P36" s="41" t="n"/>
+      <c r="Q36" s="41" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N37" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O37" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P37" s="41" t="inlineStr"/>
+      <c r="Q37" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N38" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O38" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P38" s="41" t="n"/>
+      <c r="Q38" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O34"/>
-  <conditionalFormatting sqref="K2:K34">
+  <autoFilter ref="A1:O38"/>
+  <conditionalFormatting sqref="K2:K38">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
@@ -26729,12 +27076,12 @@
       </c>
       <c r="E28" s="44" t="inlineStr">
         <is>
-          <t>room 0.01 (sklad) — items: HSV1.005, HSV2.005, PSV77.001</t>
+          <t>room 0.01 (sklad) — items: HSV1.005, HSV2.005, PSV77.001, HSV1.007</t>
         </is>
       </c>
       <c r="F28" s="44" t="inlineStr">
         <is>
-          <t>17.60 m²</t>
+          <t>23.60 m²</t>
         </is>
       </c>
       <c r="G28" s="44" t="inlineStr">
@@ -26817,7 +27164,7 @@
       </c>
       <c r="F30" s="44" t="inlineStr">
         <is>
-          <t>46.50 m²</t>
+          <t>62.50 m²</t>
         </is>
       </c>
       <c r="G30" s="44" t="inlineStr">
@@ -26857,7 +27204,7 @@
       </c>
       <c r="F31" s="44" t="inlineStr">
         <is>
-          <t>46.50 m²</t>
+          <t>62.50 m²</t>
         </is>
       </c>
       <c r="G31" s="44" t="inlineStr">
@@ -27352,7 +27699,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)…</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu…</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (121 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 134 řádků.</t>
+          <t>HSV položkově (130 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 143 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 37 sklad = 238 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 46 sklad = 247 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>238 (201 dum + 37 sklad)</t>
+          <t>247 (201 dum + 46 sklad)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 121 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
+          <t>HSV 130 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 32 | 0.85: 45 | 0.80: 21 | 0.75: 70 | 0.70: 7 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 9 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 161 needs_production_lookup (67.6 %)</t>
+          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 170 needs_production_lookup (68.8 %)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>34 items (viz Otazky_pro_Karla docx)</t>
+          <t>37 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1182,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-238 položek celkem (201 dum + 37 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 32×0.90 · 45×0.85 · 21×0.80 · 70×0.75 · 7×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+247 položek celkem (201 dum + 46 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 9×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1255,7 +1255,7 @@
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>• Total items: 238 (201 dům + 37 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 72 items s realizuje_skladbu.</t>
+          <t>• Total items: 247 (201 dům + 46 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 74 items s realizuje_skladbu.</t>
         </is>
       </c>
     </row>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Sejmutí stávající zídky + schodiště; Hloubení figury skladu; Hloubení rýh pro pasy; Hloubení parkingových patek; … (+4 dalších)</t>
+          <t>Sejmutí stávající zídky + schodiště; Hloubení figury skladu; Hloubení rýh pro pasy; Hloubení parkingových patek; … (+6 dalších)</t>
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="10" t="n"/>
       <c r="F2" s="10" t="n"/>
@@ -3106,11 +3106,11 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa; Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Schodiště prefa stupně; Vjezd Dvořákova — napojení na komunikaci; Vjezd — pískové lože; Vjezd — štěrkový podklad; … (+5 dalších)</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
@@ -3207,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="F59" s="22" t="n">
-        <v>36.74</v>
+        <v>31</v>
       </c>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="F60" s="22" t="n">
-        <v>21.209</v>
+        <v>18.1</v>
       </c>
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n"/>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="F61" s="22" t="n">
-        <v>22.26945</v>
+        <v>19</v>
       </c>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n"/>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Schodiště prefa stupně — Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -7930,7 +7930,9 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F118" s="22" t="n"/>
+      <c r="F118" s="22" t="n">
+        <v>7</v>
+      </c>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="8" t="inlineStr">
@@ -8113,34 +8115,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C123" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
+          <t>Vjezd — pískové lože — Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F123" s="22" t="n">
+        <v>0.28</v>
       </c>
       <c r="G123" s="10" t="n"/>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 564751111</t>
         </is>
       </c>
     </row>
@@ -8153,34 +8155,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C124" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Vjezd — štěrkový podklad — Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F124" s="22" t="n">
+        <v>1.05</v>
       </c>
       <c r="G124" s="10" t="n"/>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 564861111</t>
         </is>
       </c>
     </row>
@@ -8193,34 +8195,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C125" s="21" t="inlineStr">
-        <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>Odvodňovací žlab — Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="F125" s="22" t="n">
+        <v>7.775</v>
       </c>
       <c r="G125" s="10" t="n"/>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8230,37 +8232,37 @@
       </c>
       <c r="B126" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C126" s="21" t="inlineStr">
-        <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>Odvodňovací žlab — podkladní beton — Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F126" s="22" t="n">
+        <v>0.47</v>
       </c>
       <c r="G126" s="10" t="n"/>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273321411</t>
         </is>
       </c>
     </row>
@@ -8270,37 +8272,37 @@
       </c>
       <c r="B127" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C127" s="21" t="inlineStr">
-        <is>
-          <t>M-24</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>Okapový žlab — Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F127" s="9" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="F127" s="22" t="n">
+        <v>6</v>
       </c>
       <c r="G127" s="10" t="n"/>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8310,37 +8312,37 @@
       </c>
       <c r="B128" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C128" s="21" t="inlineStr">
-        <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>Trubka u pasu — vysoký pas — Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvětrání radonu (OVĚŘIT)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F128" s="9" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="F128" s="22" t="n">
+        <v>6.35</v>
       </c>
       <c r="G128" s="10" t="n"/>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8350,37 +8352,37 @@
       </c>
       <c r="B129" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C129" s="21" t="inlineStr">
-        <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>Trubka u pasu — podél stěny — Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání radonu (OVĚŘIT)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F129" s="9" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="F129" s="22" t="n">
+        <v>6.01</v>
       </c>
       <c r="G129" s="10" t="n"/>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8390,37 +8392,37 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C130" s="21" t="inlineStr">
-        <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>Schodiště — podkladní deska — Podkladní betonová deska pod prefa schodiště S05</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F130" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F130" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="G130" s="10" t="n"/>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273313611</t>
         </is>
       </c>
     </row>
@@ -8430,37 +8432,37 @@
       </c>
       <c r="B131" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C131" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>Schodiště — kladecí beton — Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F131" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F131" s="22" t="n">
+        <v>0.28</v>
       </c>
       <c r="G131" s="10" t="n"/>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8470,17 +8472,17 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C132" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
@@ -8510,17 +8512,17 @@
       </c>
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C133" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
@@ -8550,17 +8552,17 @@
       </c>
       <c r="B134" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C134" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
@@ -8595,12 +8597,12 @@
       </c>
       <c r="C135" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E135" s="20" t="inlineStr">
@@ -8624,8 +8626,368 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="20" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C136" s="21" t="inlineStr">
+        <is>
+          <t>M-24</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+        </is>
+      </c>
+      <c r="E136" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="10" t="n"/>
+      <c r="H136" s="10" t="n"/>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J136" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C137" s="21" t="inlineStr">
+        <is>
+          <t>PSV-71 — Izolace HI + TI</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+        </is>
+      </c>
+      <c r="E137" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="10" t="n"/>
+      <c r="H137" s="10" t="n"/>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J137" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C138" s="21" t="inlineStr">
+        <is>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+        </is>
+      </c>
+      <c r="E138" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="10" t="n"/>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J138" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C139" s="21" t="inlineStr">
+        <is>
+          <t>PSV-73 — Vytápění + komín</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+        </is>
+      </c>
+      <c r="E139" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="10" t="n"/>
+      <c r="H139" s="10" t="n"/>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J139" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C140" s="21" t="inlineStr">
+        <is>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+        </is>
+      </c>
+      <c r="E140" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="10" t="n"/>
+      <c r="H140" s="10" t="n"/>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J140" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C141" s="21" t="inlineStr">
+        <is>
+          <t>PSV-77 — Podlahy</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+        </is>
+      </c>
+      <c r="E141" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="10" t="n"/>
+      <c r="H141" s="10" t="n"/>
+      <c r="I141" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J141" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C142" s="21" t="inlineStr">
+        <is>
+          <t>PSV-78 — Povrchové úpravy</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="10" t="n"/>
+      <c r="I142" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J142" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C143" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E143" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="10" t="n"/>
+      <c r="H143" s="10" t="n"/>
+      <c r="I143" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J143" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C144" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="10" t="n"/>
+      <c r="H144" s="10" t="n"/>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J144" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J135"/>
+  <autoFilter ref="A1:J144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22467,11 +22829,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
@@ -23131,67 +23493,63 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>HSV-2 Základové a ŽB</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy sklad</t>
-        </is>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
-        <is>
-          <t>271313??? ?</t>
+          <t>Trubka u pasu — vysoký pas</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
+          <t>Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvětrání radonu (OVĚŘIT)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G10" s="22" t="n">
-        <v>4.84</v>
+        <v>6.35</v>
       </c>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ + TZ statika sklad §4 — C16/20 XC0 pasy 500×500</t>
+          <t>řez A-A — kroužek trubky u pasu; účel + Ø NEpopsáno → OVĚŘIT</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O10" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P10" s="41" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
+          <t>#39</t>
+        </is>
+      </c>
+      <c r="O10" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P10" s="41" t="inlineStr"/>
       <c r="Q10" s="41" t="n"/>
     </row>
     <row r="11">
@@ -23200,55 +23558,55 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>HSV-2 Základové a ŽB</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — spodní</t>
+          <t>Trubka u pasu — podél stěny</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>273313811</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
+          <t>Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání radonu (OVĚŘIT)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>6</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>6.01</v>
       </c>
       <c r="H11" s="10" t="n"/>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
+          <t>řez — druhá trubka u pasu; účel + Ø NEpopsáno → OVĚŘIT</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>#39</t>
         </is>
       </c>
       <c r="O11" s="26" t="inlineStr">
@@ -23256,12 +23614,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P11" s="41" t="n"/>
-      <c r="Q11" s="41" t="inlineStr">
-        <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P11" s="41" t="inlineStr"/>
+      <c r="Q11" s="41" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -23274,26 +23628,26 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — horní</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>311233812</t>
+          <t>Základové pasy sklad</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>271313??? ?</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>6</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>4.84</v>
       </c>
       <c r="H12" s="10" t="n"/>
       <c r="I12" s="10" t="n"/>
@@ -23307,12 +23661,12 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
+          <t>DXF sklad_DPZ + TZ statika sklad §4 — C16/20 XC0 pasy 500×500</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -23320,17 +23674,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O12" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P12" s="41" t="n"/>
-      <c r="Q12" s="41" t="inlineStr">
-        <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="O12" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P12" s="41" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S03b_sklad</t>
+        </is>
+      </c>
+      <c r="Q12" s="41" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -23343,26 +23697,26 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Beton patek + zídek — zalití</t>
+          <t>Patky parking — spodní</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>273321321</t>
+          <t>273313811</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
+          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>1.75</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>6</v>
       </c>
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n"/>
@@ -23372,21 +23726,21 @@
         </is>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 (6 patek)</t>
+          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O13" s="26" t="inlineStr">
@@ -23412,32 +23766,32 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože</t>
+          <t>Patky parking — horní</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>174101101</t>
+          <t>311233812</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>1.76</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>6</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>zemni_prace</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
@@ -23445,12 +23799,12 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_cross_discipline_legitimate</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>DXF + TZ statika sklad</t>
+          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23463,14 +23817,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P14" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad, S05_sklad</t>
-        </is>
-      </c>
+      <c r="P14" s="41" t="n"/>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>W1_PODLAHA_17.6_2026-06-01</t>
+          <t>PATKY_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23485,17 +23835,17 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Schodišťová deska + pas</t>
+          <t>Beton patek + zídek — zalití</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273321321</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -23504,7 +23854,7 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
@@ -23523,7 +23873,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — prefa schodové dílce + ŽB pas</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec 2 řady nad 6 patkami, šířka tvárnic 300 mm</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23536,12 +23886,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P15" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
-      <c r="Q15" s="41" t="n"/>
+      <c r="P15" s="41" t="n"/>
+      <c r="Q15" s="41" t="inlineStr">
+        <is>
+          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -23549,50 +23899,50 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna</t>
+          <t>Štěrkopískové lože</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>311233815</t>
+          <t>174101101</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="n">
-        <v>18</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>1.76</v>
       </c>
       <c r="H16" s="10" t="n"/>
       <c r="I16" s="10" t="n"/>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_cross_discipline_legitimate</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+          <t>DXF + TZ statika sklad</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -23607,12 +23957,12 @@
       </c>
       <c r="P16" s="41" t="inlineStr">
         <is>
-          <t>S04_sklad</t>
+          <t>S01_sklad, S05_sklad</t>
         </is>
       </c>
       <c r="Q16" s="41" t="inlineStr">
         <is>
-          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
+          <t>W1_PODLAHA_17.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23622,41 +23972,41 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu</t>
+          <t>Schodišťová deska + pas</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>311233811</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
+          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>62.5</v>
+        <v>0.8</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -23665,7 +24015,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
+          <t>TZ statika sklad §4 — prefa schodové dílce + ŽB pas</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -23680,14 +24030,10 @@
       </c>
       <c r="P17" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="Q17" s="41" t="inlineStr">
-        <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
-        </is>
-      </c>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q17" s="41" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -23700,49 +24046,50 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>1875</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>18</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M18" s="8">
-        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
-        <v/>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+        </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O18" s="26" t="inlineStr">
@@ -23752,12 +24099,12 @@
       </c>
       <c r="P18" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S04_sklad</t>
         </is>
       </c>
       <c r="Q18" s="41" t="inlineStr">
         <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
+          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23772,17 +24119,17 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
+          <t>Tvarovky ZB obvod skladu</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311233811</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -23791,17 +24138,17 @@
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
@@ -23810,7 +24157,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -23825,12 +24172,12 @@
       </c>
       <c r="P19" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q19" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23845,50 +24192,49 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
+          <t>Výztuž ZB tvarovek</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04</t>
-        </is>
+          <t>family_verified_leaf_needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M20" s="8">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="O20" s="26" t="inlineStr">
@@ -23898,12 +24244,12 @@
       </c>
       <c r="P20" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q20" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23913,41 +24259,41 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>36.74</v>
+        <v>33</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
@@ -23956,7 +24302,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -23971,12 +24317,12 @@
       </c>
       <c r="P21" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q21" s="41" t="inlineStr">
         <is>
-          <t>DS3_STROPNICE_11_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23986,22 +24332,22 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -24010,17 +24356,17 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>21.209</v>
+        <v>33</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
@@ -24029,7 +24375,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -24044,10 +24390,14 @@
       </c>
       <c r="P22" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="Q22" s="41" t="n"/>
+          <t>S03a_sklad, S04_sklad</t>
+        </is>
+      </c>
+      <c r="Q22" s="41" t="inlineStr">
+        <is>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n">
@@ -24060,36 +24410,36 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>22.26945</v>
+        <v>31</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
@@ -24098,7 +24448,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — HI souvrství</t>
+          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -24116,7 +24466,11 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q23" s="41" t="n"/>
+      <c r="Q23" s="41" t="inlineStr">
+        <is>
+          <t>TRAMY_10ks_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="n">
@@ -24129,50 +24483,49 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
-        </is>
+      <c r="M24" s="8">
+        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
+        <v/>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O24" s="26" t="inlineStr">
@@ -24187,7 +24540,7 @@
       </c>
       <c r="Q24" s="41" t="inlineStr">
         <is>
-          <t>IPE_7to6_DRAWING_2026-06-01</t>
+          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24202,17 +24555,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -24221,27 +24574,26 @@
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
-        </is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M25" s="8">
+        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
+        <v/>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -24260,7 +24612,7 @@
       </c>
       <c r="Q25" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>HI_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24275,17 +24627,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -24294,7 +24646,7 @@
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
@@ -24304,20 +24656,21 @@
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M26" s="8">
-        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
-        <v/>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+        </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O26" s="26" t="inlineStr">
@@ -24342,22 +24695,22 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -24366,26 +24719,26 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24400,12 +24753,12 @@
       </c>
       <c r="P27" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q27" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -24415,49 +24768,50 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="n">
+        <v>1420</v>
+      </c>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
-        </is>
+      <c r="M28" s="8">
+        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
+        <v/>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
@@ -24469,10 +24823,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P28" s="41" t="inlineStr"/>
+      <c r="P28" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
       <c r="Q28" s="41" t="inlineStr">
         <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+          <t>IPE_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24482,41 +24840,41 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Schodiště prefa stupně</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
@@ -24525,7 +24883,7 @@
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24538,8 +24896,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P29" s="41" t="n"/>
-      <c r="Q29" s="41" t="n"/>
+      <c r="P29" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q29" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="n">
@@ -24547,12 +24913,12 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Oplocení (plot)</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -24562,26 +24928,26 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
@@ -24590,12 +24956,12 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
+          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
-          <t>#37</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O30" s="26" t="inlineStr">
@@ -24604,7 +24970,11 @@
         </is>
       </c>
       <c r="P30" s="41" t="inlineStr"/>
-      <c r="Q30" s="41" t="n"/>
+      <c r="Q30" s="41" t="inlineStr">
+        <is>
+          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="20" t="n">
@@ -24612,41 +24982,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí stání</t>
+          <t>Vjezd — pískové lože</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564751111</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>18.5</v>
+        <v>0.28</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -24655,12 +25025,12 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
-          <t>#38</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O31" s="26" t="inlineStr">
@@ -24677,41 +25047,41 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Vjezd — štěrkový podklad</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564861111</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G32" s="23" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>1.05</v>
       </c>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
@@ -24720,7 +25090,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -24734,11 +25104,7 @@
         </is>
       </c>
       <c r="P32" s="41" t="inlineStr"/>
-      <c r="Q32" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="Q32" s="41" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n">
@@ -24746,50 +25112,50 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D33" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Odvodňovací žlab</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>23.6</v>
+        <v>7.775</v>
       </c>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K33" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L33" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
+          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -24797,21 +25163,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O33" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P33" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q33" s="41" t="inlineStr">
-        <is>
-          <t>S01_AREA_23.6_2026-06-01</t>
-        </is>
-      </c>
+      <c r="O33" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P33" s="41" t="inlineStr"/>
+      <c r="Q33" s="41" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="20" t="n">
@@ -24819,41 +25177,41 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Odvodňovací žlab — podkladní beton</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>273321411</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>0.47</v>
       </c>
       <c r="H34" s="10" t="n"/>
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K34" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L34" s="20" t="inlineStr">
         <is>
@@ -24862,7 +25220,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -24875,7 +25233,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P34" s="41" t="n"/>
+      <c r="P34" s="41" t="inlineStr"/>
       <c r="Q34" s="41" t="n"/>
     </row>
     <row r="35">
@@ -24884,41 +25242,41 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
+          <t>Okapový žlab</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n"/>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K35" s="24" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="L35" s="20" t="inlineStr">
         <is>
@@ -24927,7 +25285,7 @@
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -24940,7 +25298,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P35" s="41" t="n"/>
+      <c r="P35" s="41" t="inlineStr"/>
       <c r="Q35" s="41" t="n"/>
     </row>
     <row r="36">
@@ -24949,41 +25307,41 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Schodiště — podkladní deska</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>273313611</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H36" s="10" t="n"/>
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K36" s="24" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
@@ -24992,12 +25350,12 @@
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>skladba S05 — podkladní betonová deska</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O36" s="26" t="inlineStr">
@@ -25005,7 +25363,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P36" s="41" t="n"/>
+      <c r="P36" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q36" s="41" t="n"/>
     </row>
     <row r="37">
@@ -25014,12 +25376,12 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+          <t>Schodiště — kladecí beton</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -25029,22 +25391,22 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>0.28</v>
       </c>
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="10" t="n"/>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K37" s="24" t="n">
@@ -25057,12 +25419,12 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O37" s="26" t="inlineStr">
@@ -25070,12 +25432,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P37" s="41" t="inlineStr"/>
-      <c r="Q37" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P37" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q37" s="41" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="20" t="n">
@@ -25083,27 +25445,27 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G38" s="23" t="n">
@@ -25113,11 +25475,11 @@
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
@@ -25126,7 +25488,7 @@
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
@@ -25142,9 +25504,610 @@
       <c r="P38" s="41" t="n"/>
       <c r="Q38" s="41" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Oplocení (plot)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>zamecnik</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="N39" s="20" t="inlineStr">
+        <is>
+          <t>#37</t>
+        </is>
+      </c>
+      <c r="O39" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P39" s="41" t="inlineStr"/>
+      <c r="Q39" s="41" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Zábradlí stání</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>zamecnik</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L40" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="N40" s="20" t="inlineStr">
+        <is>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="O40" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P40" s="41" t="inlineStr"/>
+      <c r="Q40" s="41" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnictví</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Vjezdová brána</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>zamecnik</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01)</t>
+        </is>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O41" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P41" s="41" t="inlineStr"/>
+      <c r="Q41" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D42" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>podlahar</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L42" s="20" t="inlineStr">
+        <is>
+          <t>wrong_leaf_disambiguation_needed</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
+        </is>
+      </c>
+      <c r="N42" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O42" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P42" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q42" s="41" t="inlineStr">
+        <is>
+          <t>S01_AREA_23.6_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>031032000</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>prefa_bloky_specialista</t>
+        </is>
+      </c>
+      <c r="K43" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L43" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+        </is>
+      </c>
+      <c r="N43" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O43" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P43" s="41" t="n"/>
+      <c r="Q43" s="41" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace odpadu sklad</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>997013211</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>bourani_demolice</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+        </is>
+      </c>
+      <c r="N44" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O44" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P44" s="41" t="n"/>
+      <c r="Q44" s="41" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>030141000</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+        </is>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O45" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P45" s="41" t="n"/>
+      <c r="Q45" s="41" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O46" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P46" s="41" t="inlineStr"/>
+      <c r="Q46" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M47" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N47" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O47" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P47" s="41" t="n"/>
+      <c r="Q47" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O38"/>
-  <conditionalFormatting sqref="K2:K38">
+  <autoFilter ref="A1:O47"/>
+  <conditionalFormatting sqref="K2:K47">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
@@ -27281,7 +28244,7 @@
       </c>
       <c r="E33" s="44" t="inlineStr">
         <is>
-          <t>room 1.02 (mezipodesta schodiště) — items: HSV2.005, HSV2.006, HSV5.001</t>
+          <t>room 1.02 (mezipodesta schodiště) — items: HSV2.005, HSV2.006, HSV5.001, HSV5.008, HSV5.009</t>
         </is>
       </c>
       <c r="F33" s="44" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — horní — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking — horní — Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -23820,7 +23820,7 @@
       <c r="P14" s="41" t="n"/>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+          <t>TVARNICE_SPLIT_FIX_2026-06-02 — materiál-leg byl chybně ocel S235 (auto-split chytil IPE180); ztracené bednění → komplet</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (130 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 143 řádků.</t>
+          <t>HSV položkově (132 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 145 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 46 sklad = 247 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 48 sklad = 249 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>247 (201 dum + 46 sklad)</t>
+          <t>249 (201 dum + 48 sklad)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 130 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
+          <t>HSV 132 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 9 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
+          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 11 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 170 needs_production_lookup (68.8 %)</t>
+          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 172 needs_production_lookup (69.1 %)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>37 items (viz Otazky_pro_Karla docx)</t>
+          <t>38 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1182,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-247 položek celkem (201 dum + 46 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 9×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
+249 položek celkem (201 dum + 48 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 11×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1255,7 +1255,7 @@
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>• Total items: 247 (201 dům + 46 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 74 items s realizuje_skladbu.</t>
+          <t>• Total items: 249 (201 dům + 48 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 74 items s realizuje_skladbu.</t>
         </is>
       </c>
     </row>
@@ -3031,11 +3031,11 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy sklad; Patky parking — spodní; Patky parking — horní; Beton patek + zídek — zalití; … (+2 dalších)</t>
+          <t>Základové pasy sklad; Patky parking — spodní; Patky parking — horní; Beton patek + zídek — zalití; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="10" t="n"/>
@@ -3207,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
@@ -8475,34 +8475,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C132" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
+          <t>Bednění základů (pasy + patky spodní) — Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F132" s="22" t="n">
+        <v>25.4</v>
       </c>
       <c r="G132" s="10" t="n"/>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273351215</t>
         </is>
       </c>
     </row>
@@ -8515,34 +8515,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C133" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Výztuž tvárnic ZB patek + věnce — Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="n">
-        <v>1</v>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>153</v>
       </c>
       <c r="G133" s="10" t="n"/>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zelezarsky</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273361821</t>
         </is>
       </c>
     </row>
@@ -8557,12 +8557,12 @@
       </c>
       <c r="C134" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
@@ -8592,17 +8592,17 @@
       </c>
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C135" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E135" s="20" t="inlineStr">
@@ -8632,17 +8632,17 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C136" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
@@ -8677,12 +8677,12 @@
       </c>
       <c r="C137" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E137" s="20" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="C138" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E138" s="20" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="C139" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E139" s="20" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="C140" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="C141" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E141" s="20" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="C142" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E142" s="20" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="C143" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E143" s="20" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="C144" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E144" s="20" t="inlineStr">
@@ -8986,8 +8986,88 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="20" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C145" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E145" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="10" t="n"/>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J145" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C146" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="10" t="n"/>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J146" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J144"/>
+  <autoFilter ref="A1:J146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22829,7 +22909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23854,7 +23934,7 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
@@ -23873,7 +23953,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec 2 řady nad 6 patkami, šířka tvárnic 300 mm</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec délka 6.7 m (ruční obmer)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23889,7 +23969,7 @@
       <c r="P15" s="41" t="n"/>
       <c r="Q15" s="41" t="inlineStr">
         <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+          <t>VENEC_6.7_2026-06-02</t>
         </is>
       </c>
     </row>
@@ -24041,41 +24121,41 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna</t>
+          <t>Bednění základů (pasy + patky spodní)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>311233815</t>
+          <t>273351215</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+          <t>Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>18</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>25.4</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
@@ -24084,12 +24164,12 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+          <t>výkres D.1.1.02 + řez — bednění základů; podíl do rýhy vs systémové OVĚŘIT</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#42</t>
         </is>
       </c>
       <c r="O18" s="26" t="inlineStr">
@@ -24097,16 +24177,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P18" s="41" t="inlineStr">
-        <is>
-          <t>S04_sklad</t>
-        </is>
-      </c>
-      <c r="Q18" s="41" t="inlineStr">
-        <is>
-          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P18" s="41" t="inlineStr"/>
+      <c r="Q18" s="41" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -24114,41 +24186,41 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu</t>
+          <t>Výztuž tvárnic ZB patek + věnce</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>311233811</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
+          <t>Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>62.5</v>
+        <v>153</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>zelezarsky</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
@@ -24157,12 +24229,12 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
+          <t>TZ statika sklad §3 — výztuž B500B do tvárnic ZB; sazba dle stěny S03a (HSV3.003)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#42</t>
         </is>
       </c>
       <c r="O19" s="26" t="inlineStr">
@@ -24170,16 +24242,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P19" s="41" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="Q19" s="41" t="inlineStr">
-        <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P19" s="41" t="inlineStr"/>
+      <c r="Q19" s="41" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -24192,49 +24256,50 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>1875</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>18</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M20" s="8">
-        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
-        <v/>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+        </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O20" s="26" t="inlineStr">
@@ -24244,12 +24309,12 @@
       </c>
       <c r="P20" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S04_sklad</t>
         </is>
       </c>
       <c r="Q20" s="41" t="inlineStr">
         <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
+          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24264,17 +24329,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
+          <t>Tvarovky ZB obvod skladu</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311233811</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -24283,17 +24348,17 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
@@ -24302,7 +24367,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -24317,12 +24382,12 @@
       </c>
       <c r="P21" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q21" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24337,50 +24402,49 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
+          <t>Výztuž ZB tvarovek</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04</t>
-        </is>
+          <t>family_verified_leaf_needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M22" s="8">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="O22" s="26" t="inlineStr">
@@ -24390,12 +24454,12 @@
       </c>
       <c r="P22" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q22" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24405,41 +24469,41 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
@@ -24448,7 +24512,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -24463,12 +24527,12 @@
       </c>
       <c r="P23" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q23" s="41" t="inlineStr">
         <is>
-          <t>TRAMY_10ks_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24478,22 +24542,22 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -24502,26 +24566,27 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>18.1</v>
+        <v>33</v>
       </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M24" s="8">
-        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
-        <v/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
+        </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
@@ -24535,12 +24600,12 @@
       </c>
       <c r="P24" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q24" s="41" t="inlineStr">
         <is>
-          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24555,32 +24620,32 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
@@ -24591,9 +24656,10 @@
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M25" s="8">
-        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
-        <v/>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
+        </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -24612,7 +24678,7 @@
       </c>
       <c r="Q25" s="41" t="inlineStr">
         <is>
-          <t>HI_TRAMY_BASE_2026-06-01</t>
+          <t>TRAMY_10ks_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24627,50 +24693,49 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
-        </is>
+      <c r="M26" s="8">
+        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
+        <v/>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O26" s="26" t="inlineStr">
@@ -24685,7 +24750,7 @@
       </c>
       <c r="Q26" s="41" t="inlineStr">
         <is>
-          <t>IPE_7to6_DRAWING_2026-06-01</t>
+          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24700,17 +24765,17 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -24719,27 +24784,26 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
-        </is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M27" s="8">
+        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
+        <v/>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -24758,7 +24822,7 @@
       </c>
       <c r="Q27" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>HI_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24773,17 +24837,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -24792,7 +24856,7 @@
         </is>
       </c>
       <c r="G28" s="22" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
@@ -24802,20 +24866,21 @@
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M28" s="8">
-        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
-        <v/>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+        </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O28" s="26" t="inlineStr">
@@ -24840,22 +24905,22 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Schodiště prefa stupně</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -24864,26 +24929,26 @@
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24898,12 +24963,12 @@
       </c>
       <c r="P29" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q29" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -24913,51 +24978,50 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>7</v>
+        <v>1420</v>
       </c>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
-        </is>
+      <c r="M30" s="8">
+        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
+        <v/>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -24969,10 +25033,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P30" s="41" t="inlineStr"/>
+      <c r="P30" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
       <c r="Q30" s="41" t="inlineStr">
         <is>
-          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+          <t>IPE_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24982,41 +25050,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + zpevněné plochy</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Vjezd — pískové lože</t>
+          <t>Schodiště prefa stupně</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>564751111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>0.28</v>
+        <v>5.5</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -25025,7 +25093,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -25038,8 +25106,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P31" s="41" t="inlineStr"/>
-      <c r="Q31" s="41" t="n"/>
+      <c r="P31" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q31" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="n">
@@ -25047,37 +25123,37 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + zpevněné plochy</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Vjezd — štěrkový podklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>564861111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
+          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
@@ -25090,7 +25166,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -25104,7 +25180,11 @@
         </is>
       </c>
       <c r="P32" s="41" t="inlineStr"/>
-      <c r="Q32" s="41" t="n"/>
+      <c r="Q32" s="41" t="inlineStr">
+        <is>
+          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n">
@@ -25117,26 +25197,26 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Odvodňovací žlab</t>
+          <t>Vjezd — pískové lože</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564751111</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>7.775</v>
+        <v>0.28</v>
       </c>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
@@ -25155,7 +25235,7 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -25182,17 +25262,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Odvodňovací žlab — podkladní beton</t>
+          <t>Vjezd — štěrkový podklad</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>273321411</t>
+          <t>564861111</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -25201,7 +25281,7 @@
         </is>
       </c>
       <c r="G34" s="22" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="H34" s="10" t="n"/>
       <c r="I34" s="10" t="n"/>
@@ -25220,7 +25300,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -25247,7 +25327,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Okapový žlab</t>
+          <t>Odvodňovací žlab</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -25257,7 +25337,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -25266,7 +25346,7 @@
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>6</v>
+        <v>7.775</v>
       </c>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n"/>
@@ -25276,7 +25356,7 @@
         </is>
       </c>
       <c r="K35" s="24" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="L35" s="20" t="inlineStr">
         <is>
@@ -25285,7 +25365,7 @@
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
+          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -25312,36 +25392,36 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Schodiště — podkladní deska</t>
+          <t>Odvodňovací žlab — podkladní beton</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>273313611</t>
+          <t>273321411</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Podkladní betonová deska pod prefa schodiště S05</t>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G36" s="22" t="n">
-        <v>5.5</v>
+        <v>0.47</v>
       </c>
       <c r="H36" s="10" t="n"/>
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K36" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
@@ -25350,12 +25430,12 @@
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>skladba S05 — podkladní betonová deska</t>
+          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O36" s="26" t="inlineStr">
@@ -25363,11 +25443,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P36" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="P36" s="41" t="inlineStr"/>
       <c r="Q36" s="41" t="n"/>
     </row>
     <row r="37">
@@ -25381,7 +25457,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Schodiště — kladecí beton</t>
+          <t>Okapový žlab</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -25391,16 +25467,16 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>0.28</v>
+        <v>6</v>
       </c>
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="10" t="n"/>
@@ -25410,7 +25486,7 @@
         </is>
       </c>
       <c r="K37" s="24" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="L37" s="20" t="inlineStr">
         <is>
@@ -25419,12 +25495,12 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
+          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O37" s="26" t="inlineStr">
@@ -25432,11 +25508,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P37" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="P37" s="41" t="inlineStr"/>
       <c r="Q37" s="41" t="n"/>
     </row>
     <row r="38">
@@ -25445,41 +25517,41 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Schodiště — podkladní deska</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>273313611</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H38" s="10" t="n"/>
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
@@ -25488,12 +25560,12 @@
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>skladba S05 — podkladní betonová deska</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O38" s="26" t="inlineStr">
@@ -25501,7 +25573,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P38" s="41" t="n"/>
+      <c r="P38" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q38" s="41" t="n"/>
     </row>
     <row r="39">
@@ -25510,12 +25586,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Oplocení (plot)</t>
+          <t>Schodiště — kladecí beton</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -25525,22 +25601,22 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G39" s="22" t="n">
-        <v>3.8</v>
+        <v>0.28</v>
       </c>
       <c r="H39" s="10" t="n"/>
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K39" s="24" t="n">
@@ -25553,12 +25629,12 @@
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
+          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>#37</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O39" s="26" t="inlineStr">
@@ -25566,7 +25642,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P39" s="41" t="inlineStr"/>
+      <c r="P39" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q39" s="41" t="n"/>
     </row>
     <row r="40">
@@ -25575,41 +25655,41 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí stání</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="n">
-        <v>18.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H40" s="10" t="n"/>
       <c r="I40" s="10" t="n"/>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K40" s="24" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="L40" s="20" t="inlineStr">
         <is>
@@ -25618,12 +25698,12 @@
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>#38</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O40" s="26" t="inlineStr">
@@ -25631,7 +25711,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P40" s="41" t="inlineStr"/>
+      <c r="P40" s="41" t="n"/>
       <c r="Q40" s="41" t="n"/>
     </row>
     <row r="41">
@@ -25640,12 +25720,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Oplocení (plot)</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -25655,16 +25735,16 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>3.8</v>
       </c>
       <c r="H41" s="10" t="n"/>
       <c r="I41" s="10" t="n"/>
@@ -25674,7 +25754,7 @@
         </is>
       </c>
       <c r="K41" s="24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L41" s="20" t="inlineStr">
         <is>
@@ -25683,12 +25763,12 @@
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#37</t>
         </is>
       </c>
       <c r="O41" s="26" t="inlineStr">
@@ -25697,11 +25777,7 @@
         </is>
       </c>
       <c r="P41" s="41" t="inlineStr"/>
-      <c r="Q41" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="Q41" s="41" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
@@ -25709,72 +25785,64 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D42" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Zábradlí stání</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G42" s="22" t="n">
-        <v>23.6</v>
+        <v>18.5</v>
       </c>
       <c r="H42" s="10" t="n"/>
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K42" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O42" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P42" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q42" s="41" t="inlineStr">
-        <is>
-          <t>S01_AREA_23.6_2026-06-01</t>
-        </is>
-      </c>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="O42" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P42" s="41" t="inlineStr"/>
+      <c r="Q42" s="41" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
@@ -25782,27 +25850,27 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
@@ -25812,11 +25880,11 @@
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K43" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L43" s="20" t="inlineStr">
         <is>
@@ -25825,7 +25893,7 @@
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N43" s="20" t="inlineStr">
@@ -25838,8 +25906,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P43" s="41" t="n"/>
-      <c r="Q43" s="41" t="n"/>
+      <c r="P43" s="41" t="inlineStr"/>
+      <c r="Q43" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
@@ -25847,50 +25919,50 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G44" s="22" t="n">
-        <v>8</v>
+        <v>23.6</v>
       </c>
       <c r="H44" s="10" t="n"/>
       <c r="I44" s="10" t="n"/>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K44" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L44" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
         </is>
       </c>
       <c r="N44" s="20" t="inlineStr">
@@ -25898,13 +25970,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O44" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P44" s="41" t="n"/>
-      <c r="Q44" s="41" t="n"/>
+      <c r="O44" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P44" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q44" s="41" t="inlineStr">
+        <is>
+          <t>S01_AREA_23.6_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="n">
@@ -25912,22 +25992,22 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
@@ -25942,11 +26022,11 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K45" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
@@ -25955,7 +26035,7 @@
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
@@ -25977,41 +26057,41 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H46" s="10" t="n"/>
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K46" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
@@ -26020,7 +26100,7 @@
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
@@ -26033,12 +26113,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P46" s="41" t="inlineStr"/>
-      <c r="Q46" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P46" s="41" t="n"/>
+      <c r="Q46" s="41" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="20" t="n">
@@ -26046,27 +26122,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Geodetické vytýčení sklad</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
@@ -26076,11 +26152,11 @@
       <c r="I47" s="10" t="n"/>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K47" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L47" s="20" t="inlineStr">
         <is>
@@ -26089,7 +26165,7 @@
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
@@ -26105,9 +26181,143 @@
       <c r="P47" s="41" t="n"/>
       <c r="Q47" s="41" t="n"/>
     </row>
+    <row r="48">
+      <c r="A48" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L48" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O48" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P48" s="41" t="inlineStr"/>
+      <c r="Q48" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K49" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O49" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P49" s="41" t="n"/>
+      <c r="Q49" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O47"/>
-  <conditionalFormatting sqref="K2:K47">
+  <autoFilter ref="A1:O49"/>
+  <conditionalFormatting sqref="K2:K49">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2_final.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (130 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 143 řádků.</t>
+          <t>HSV položkově (132 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 145 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 46 sklad = 247 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 48 sklad = 249 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>247 (201 dum + 46 sklad)</t>
+          <t>249 (201 dum + 48 sklad)</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 130 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
+          <t>HSV 132 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 9 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
+          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 11 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 170 needs_production_lookup (68.8 %)</t>
+          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 172 needs_production_lookup (69.1 %)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>37 items (viz Otazky_pro_Karla docx)</t>
+          <t>38 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1182,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-247 položek celkem (201 dum + 46 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 9×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
+249 položek celkem (201 dum + 48 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 11×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -1255,7 +1255,7 @@
     <row r="55">
       <c r="A55" s="45" t="inlineStr">
         <is>
-          <t>• Total items: 247 (201 dům + 46 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 74 items s realizuje_skladbu.</t>
+          <t>• Total items: 249 (201 dům + 48 sklad) — vč. CEV +3 (komín/zídky/drenáž), anchor-gap +2 (přesun hmot/lešení), terasa-area fix + venkovní schody na terénu. 74 items s realizuje_skladbu.</t>
         </is>
       </c>
     </row>
@@ -3031,11 +3031,11 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy sklad; Patky parking — spodní; Patky parking — horní; Beton patek + zídek — zalití; … (+2 dalších)</t>
+          <t>Základové pasy sklad; Patky parking — spodní; Patky parking — horní; Beton patek + zídek — zalití; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="10" t="n"/>
@@ -3207,7 +3207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — horní — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking — horní — Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
@@ -8475,34 +8475,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C132" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
+          <t>Bednění základů (pasy + patky spodní) — Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F132" s="22" t="n">
+        <v>25.4</v>
       </c>
       <c r="G132" s="10" t="n"/>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273351215</t>
         </is>
       </c>
     </row>
@@ -8515,34 +8515,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C133" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Výztuž tvárnic ZB patek + věnce — Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="n">
-        <v>1</v>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>153</v>
       </c>
       <c r="G133" s="10" t="n"/>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zelezarsky</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273361821</t>
         </is>
       </c>
     </row>
@@ -8557,12 +8557,12 @@
       </c>
       <c r="C134" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
@@ -8592,17 +8592,17 @@
       </c>
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C135" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E135" s="20" t="inlineStr">
@@ -8632,17 +8632,17 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C136" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
@@ -8677,12 +8677,12 @@
       </c>
       <c r="C137" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E137" s="20" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="C138" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E138" s="20" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="C139" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E139" s="20" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="C140" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="C141" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E141" s="20" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="C142" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E142" s="20" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="C143" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E143" s="20" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="C144" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E144" s="20" t="inlineStr">
@@ -8986,8 +8986,88 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="20" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C145" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E145" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="10" t="n"/>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J145" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C146" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="10" t="n"/>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J146" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J144"/>
+  <autoFilter ref="A1:J146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22829,7 +22909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23776,7 +23856,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -23820,7 +23900,7 @@
       <c r="P14" s="41" t="n"/>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+          <t>TVARNICE_SPLIT_FIX_2026-06-02 — materiál-leg byl chybně ocel S235 (auto-split chytil IPE180); ztracené bednění → komplet</t>
         </is>
       </c>
     </row>
@@ -23854,7 +23934,7 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
@@ -23873,7 +23953,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec 2 řady nad 6 patkami, šířka tvárnic 300 mm</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec délka 6.7 m (ruční obmer)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23889,7 +23969,7 @@
       <c r="P15" s="41" t="n"/>
       <c r="Q15" s="41" t="inlineStr">
         <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+          <t>VENEC_6.7_2026-06-02</t>
         </is>
       </c>
     </row>
@@ -24041,41 +24121,41 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna</t>
+          <t>Bednění základů (pasy + patky spodní)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>311233815</t>
+          <t>273351215</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+          <t>Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>18</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>25.4</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
@@ -24084,12 +24164,12 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+          <t>výkres D.1.1.02 + řez — bednění základů; podíl do rýhy vs systémové OVĚŘIT</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#42</t>
         </is>
       </c>
       <c r="O18" s="26" t="inlineStr">
@@ -24097,16 +24177,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P18" s="41" t="inlineStr">
-        <is>
-          <t>S04_sklad</t>
-        </is>
-      </c>
-      <c r="Q18" s="41" t="inlineStr">
-        <is>
-          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P18" s="41" t="inlineStr"/>
+      <c r="Q18" s="41" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -24114,41 +24186,41 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu</t>
+          <t>Výztuž tvárnic ZB patek + věnce</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>311233811</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
+          <t>Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>62.5</v>
+        <v>153</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>zelezarsky</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
@@ -24157,12 +24229,12 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
+          <t>TZ statika sklad §3 — výztuž B500B do tvárnic ZB; sazba dle stěny S03a (HSV3.003)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#42</t>
         </is>
       </c>
       <c r="O19" s="26" t="inlineStr">
@@ -24170,16 +24242,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P19" s="41" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="Q19" s="41" t="inlineStr">
-        <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P19" s="41" t="inlineStr"/>
+      <c r="Q19" s="41" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -24192,49 +24256,50 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>1875</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>18</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M20" s="8">
-        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
-        <v/>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+        </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O20" s="26" t="inlineStr">
@@ -24244,12 +24309,12 @@
       </c>
       <c r="P20" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S04_sklad</t>
         </is>
       </c>
       <c r="Q20" s="41" t="inlineStr">
         <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
+          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24264,17 +24329,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
+          <t>Tvarovky ZB obvod skladu</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311233811</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -24283,17 +24348,17 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
@@ -24302,7 +24367,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -24317,12 +24382,12 @@
       </c>
       <c r="P21" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q21" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24337,50 +24402,49 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
+          <t>Výztuž ZB tvarovek</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04</t>
-        </is>
+          <t>family_verified_leaf_needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M22" s="8">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="O22" s="26" t="inlineStr">
@@ -24390,12 +24454,12 @@
       </c>
       <c r="P22" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q22" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24405,41 +24469,41 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
@@ -24448,7 +24512,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -24463,12 +24527,12 @@
       </c>
       <c r="P23" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q23" s="41" t="inlineStr">
         <is>
-          <t>TRAMY_10ks_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24478,22 +24542,22 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -24502,26 +24566,27 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>18.1</v>
+        <v>33</v>
       </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M24" s="8">
-        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
-        <v/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
+        </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
@@ -24535,12 +24600,12 @@
       </c>
       <c r="P24" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q24" s="41" t="inlineStr">
         <is>
-          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24555,32 +24620,32 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
@@ -24591,9 +24656,10 @@
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M25" s="8">
-        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
-        <v/>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
+        </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -24612,7 +24678,7 @@
       </c>
       <c r="Q25" s="41" t="inlineStr">
         <is>
-          <t>HI_TRAMY_BASE_2026-06-01</t>
+          <t>TRAMY_10ks_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24627,50 +24693,49 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
-        </is>
+      <c r="M26" s="8">
+        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
+        <v/>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O26" s="26" t="inlineStr">
@@ -24685,7 +24750,7 @@
       </c>
       <c r="Q26" s="41" t="inlineStr">
         <is>
-          <t>IPE_7to6_DRAWING_2026-06-01</t>
+          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24700,17 +24765,17 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -24719,27 +24784,26 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
-        </is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M27" s="8">
+        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
+        <v/>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -24758,7 +24822,7 @@
       </c>
       <c r="Q27" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>HI_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24773,17 +24837,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -24792,7 +24856,7 @@
         </is>
       </c>
       <c r="G28" s="22" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
@@ -24802,20 +24866,21 @@
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M28" s="8">
-        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
-        <v/>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+        </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O28" s="26" t="inlineStr">
@@ -24840,22 +24905,22 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Schodiště prefa stupně</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -24864,26 +24929,26 @@
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24898,12 +24963,12 @@
       </c>
       <c r="P29" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q29" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -24913,51 +24978,50 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>7</v>
+        <v>1420</v>
       </c>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
-        </is>
+      <c r="M30" s="8">
+        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
+        <v/>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -24969,10 +25033,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P30" s="41" t="inlineStr"/>
+      <c r="P30" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
       <c r="Q30" s="41" t="inlineStr">
         <is>
-          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+          <t>IPE_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24982,41 +25050,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + zpevněné plochy</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Vjezd — pískové lože</t>
+          <t>Schodiště prefa stupně</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>564751111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>0.28</v>
+        <v>5.5</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -25025,7 +25093,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -25038,8 +25106,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P31" s="41" t="inlineStr"/>
-      <c r="Q31" s="41" t="n"/>
+      <c r="P31" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q31" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="n">
@@ -25047,37 +25123,37 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + zpevněné plochy</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Vjezd — štěrkový podklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>564861111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
+          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
@@ -25090,7 +25166,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -25104,7 +25180,11 @@
         </is>
       </c>
       <c r="P32" s="41" t="inlineStr"/>
-      <c r="Q32" s="41" t="n"/>
+      <c r="Q32" s="41" t="inlineStr">
+        <is>
+          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n">
@@ -25117,26 +25197,26 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Odvodňovací žlab</t>
+          <t>Vjezd — pískové lože</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564751111</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>7.775</v>
+        <v>0.28</v>
       </c>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
@@ -25155,7 +25235,7 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -25182,17 +25262,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Odvodňovací žlab — podkladní beton</t>
+          <t>Vjezd — štěrkový podklad</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>273321411</t>
+          <t>564861111</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -25201,7 +25281,7 @@
         </is>
       </c>
       <c r="G34" s="22" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="H34" s="10" t="n"/>
       <c r="I34" s="10" t="n"/>
@@ -25220,7 +25300,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -25247,7 +25327,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Okapový žlab</t>
+          <t>Odvodňovací žlab</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -25257,7 +25337,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -25266,7 +25346,7 @@
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>6</v>
+        <v>7.775</v>
       </c>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n"/>
@@ -25276,7 +25356,7 @@
         </is>
       </c>
       <c r="K35" s="24" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="L35" s="20" t="inlineStr">
         <is>
@@ -25285,7 +25365,7 @@
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
+          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -25312,36 +25392,36 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Schodiště — podkladní deska</t>
+          <t>Odvodňovací žlab — podkladní beton</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>273313611</t>
+          <t>273321411</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Podkladní betonová deska pod prefa schodiště S05</t>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G36" s="22" t="n">
-        <v>5.5</v>
+        <v>0.47</v>
       </c>
       <c r="H36" s="10" t="n"/>
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K36" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
@@ -25350,12 +25430,12 @@
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>skladba S05 — podkladní betonová deska</t>
+          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O36" s="26" t="inlineStr">
@@ -25363,11 +25443,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P36" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="P36" s="41" t="inlineStr"/>
       <c r="Q36" s="41" t="n"/>
     </row>
     <row r="37">
@@ -25381,7 +25457,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Schodiště — kladecí beton</t>
+          <t>Okapový žlab</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -25391,16 +25467,16 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>0.28</v>
+        <v>6</v>
       </c>
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="10" t="n"/>
@@ -25410,7 +25486,7 @@
         </is>
       </c>
       <c r="K37" s="24" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="L37" s="20" t="inlineStr">
         <is>
@@ -25419,12 +25495,12 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
+          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O37" s="26" t="inlineStr">
@@ -25432,11 +25508,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P37" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="P37" s="41" t="inlineStr"/>
       <c r="Q37" s="41" t="n"/>
     </row>
     <row r="38">
@@ -25445,41 +25517,41 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Schodiště — podkladní deska</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>273313611</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H38" s="10" t="n"/>
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
@@ -25488,12 +25560,12 @@
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>skladba S05 — podkladní betonová deska</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O38" s="26" t="inlineStr">
@@ -25501,7 +25573,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P38" s="41" t="n"/>
+      <c r="P38" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q38" s="41" t="n"/>
     </row>
     <row r="39">
@@ -25510,12 +25586,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Oplocení (plot)</t>
+          <t>Schodiště — kladecí beton</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -25525,22 +25601,22 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G39" s="22" t="n">
-        <v>3.8</v>
+        <v>0.28</v>
       </c>
       <c r="H39" s="10" t="n"/>
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K39" s="24" t="n">
@@ -25553,12 +25629,12 @@
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
+          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>#37</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O39" s="26" t="inlineStr">
@@ -25566,7 +25642,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P39" s="41" t="inlineStr"/>
+      <c r="P39" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q39" s="41" t="n"/>
     </row>
     <row r="40">
@@ -25575,41 +25655,41 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí stání</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="n">
-        <v>18.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H40" s="10" t="n"/>
       <c r="I40" s="10" t="n"/>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K40" s="24" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="L40" s="20" t="inlineStr">
         <is>
@@ -25618,12 +25698,12 @@
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>#38</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O40" s="26" t="inlineStr">
@@ -25631,7 +25711,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P40" s="41" t="inlineStr"/>
+      <c r="P40" s="41" t="n"/>
       <c r="Q40" s="41" t="n"/>
     </row>
     <row r="41">
@@ -25640,12 +25720,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Oplocení (plot)</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -25655,16 +25735,16 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>3.8</v>
       </c>
       <c r="H41" s="10" t="n"/>
       <c r="I41" s="10" t="n"/>
@@ -25674,7 +25754,7 @@
         </is>
       </c>
       <c r="K41" s="24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L41" s="20" t="inlineStr">
         <is>
@@ -25683,12 +25763,12 @@
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#37</t>
         </is>
       </c>
       <c r="O41" s="26" t="inlineStr">
@@ -25697,11 +25777,7 @@
         </is>
       </c>
       <c r="P41" s="41" t="inlineStr"/>
-      <c r="Q41" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="Q41" s="41" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
@@ -25709,72 +25785,64 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D42" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Zábradlí stání</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G42" s="22" t="n">
-        <v>23.6</v>
+        <v>18.5</v>
       </c>
       <c r="H42" s="10" t="n"/>
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K42" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O42" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P42" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q42" s="41" t="inlineStr">
-        <is>
-          <t>S01_AREA_23.6_2026-06-01</t>
-        </is>
-      </c>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="O42" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P42" s="41" t="inlineStr"/>
+      <c r="Q42" s="41" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
@@ -25782,27 +25850,27 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
@@ -25812,11 +25880,11 @@
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K43" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L43" s="20" t="inlineStr">
         <is>
@@ -25825,7 +25893,7 @@
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N43" s="20" t="inlineStr">
@@ -25838,8 +25906,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P43" s="41" t="n"/>
-      <c r="Q43" s="41" t="n"/>
+      <c r="P43" s="41" t="inlineStr"/>
+      <c r="Q43" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
@@ -25847,50 +25919,50 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G44" s="22" t="n">
-        <v>8</v>
+        <v>23.6</v>
       </c>
       <c r="H44" s="10" t="n"/>
       <c r="I44" s="10" t="n"/>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K44" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L44" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
         </is>
       </c>
       <c r="N44" s="20" t="inlineStr">
@@ -25898,13 +25970,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O44" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P44" s="41" t="n"/>
-      <c r="Q44" s="41" t="n"/>
+      <c r="O44" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P44" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q44" s="41" t="inlineStr">
+        <is>
+          <t>S01_AREA_23.6_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="n">
@@ -25912,22 +25992,22 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
@@ -25942,11 +26022,11 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K45" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
@@ -25955,7 +26035,7 @@
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
@@ -25977,41 +26057,41 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H46" s="10" t="n"/>
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K46" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
@@ -26020,7 +26100,7 @@
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
@@ -26033,12 +26113,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P46" s="41" t="inlineStr"/>
-      <c r="Q46" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P46" s="41" t="n"/>
+      <c r="Q46" s="41" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="20" t="n">
@@ -26046,27 +26122,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Geodetické vytýčení sklad</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
@@ -26076,11 +26152,11 @@
       <c r="I47" s="10" t="n"/>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K47" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L47" s="20" t="inlineStr">
         <is>
@@ -26089,7 +26165,7 @@
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
@@ -26105,9 +26181,143 @@
       <c r="P47" s="41" t="n"/>
       <c r="Q47" s="41" t="n"/>
     </row>
+    <row r="48">
+      <c r="A48" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L48" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O48" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P48" s="41" t="inlineStr"/>
+      <c r="Q48" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K49" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O49" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P49" s="41" t="n"/>
+      <c r="Q49" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O47"/>
-  <conditionalFormatting sqref="K2:K47">
+  <autoFilter ref="A1:O49"/>
+  <conditionalFormatting sqref="K2:K49">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
